--- a/excel_reports/backtest_compare/s18/compare_s18_M1_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s18/compare_s18_M1_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:54:39</t>
+          <t>2026-06-19 09:47:53</t>
         </is>
       </c>
     </row>
@@ -3678,10 +3678,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3843,66 +3843,8 @@
         <v>46177.88680555556</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>-6.36</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>46171.85972222222</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>46175.70833333334</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-6.79</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>46177.88680555556</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>46177.88680555556</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>